--- a/results_loo.xlsx
+++ b/results_loo.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.717948717948718</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>0.1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6410256410256411</v>
       </c>
     </row>
     <row r="4">
@@ -485,7 +485,7 @@
         <v>0.5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.6410256410256411</v>
+        <v>0.6923076923076923</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>0.6000000000000001</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6410256410256411</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6410256410256411</v>
+        <v>0.717948717948718</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>0.8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6410256410256411</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>0.9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.6410256410256411</v>
       </c>
     </row>
     <row r="12">
@@ -525,86 +525,6 @@
         <v>1</v>
       </c>
       <c r="B12" t="n">
-        <v>0.6410256410256411</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0.6923076923076923</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0.6410256410256411</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0.717948717948718</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.6923076923076923</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>2</v>
-      </c>
-      <c r="B22" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
